--- a/Phytium_PPE_System_SourceCode/功能测试表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能测试表.xlsx
@@ -1262,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="11.4416666666667" customWidth="1" style="24" min="1" max="1"/>
@@ -1656,80 +1656,136 @@
       <c r="F16" s="29" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>TC-09</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>主从核生命监湧</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>通信链路断连 FIT 测试</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1. 在主核运行 ppe_system 程序，启动 RPMsg 心跳线程每 500ms 发送 DEVICE_CORE_CHECK 给从核。
-2. 手动终止（或 Kill）主核安全监湧进程。
-3. 观察从核是否能在连续 4 次（2秒）未收到心跳后检测到主核失联。</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>从核判定主核死机，立即接管控制权，发出 Fail-Safe 安全信号（蜂鸣器长鸣报警）。</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Pass。经真机测试，在手动 kill 掉主控 Qt 程序后，从核串口输出心跳超时日志，并在 2.0s 内精准触发了蜂鸣器硬件级长鸣警报，主从心跳保护机制验证通过。</t>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>双核通信 Active Heartbeat 心跳测试</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>1. 主从核通过 OpenAMP 初始化成功。
+2. 心跳监控线程 heartbeat_task 已启动，周期 500ms。</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>1. 主核正常运行时，监测从核对心跳包的应答。
+2. 在主核中人为挂起 AI 业务线程，观察心跳是否能维持或检测到失联。</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>1. 正常运行时主从核以 500ms 频率稳定收发心跳包。
+2. 主核业务异常后，能在 2s 内（4次未响应）准确检测并报警，从核串口输出失联报警日志。</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Pass。真机测试表明主从核心跳收发无误。在主核人为停止心跳发送 2s 后，从核串口精准捕获失联报警，系统未发生崩溃僵死。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2. 观察从核的应答状态以及失联时的动作。</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>2. 从核检测到 2s 主核心跳丢失后，打印失联日志，开启 Fail-Safe 警报，并在 10s WDT 超时后触发冷重启。</t>
+        </is>
+      </c>
+      <c r="F18" s="29" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>TC-10</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>看门狗硬件容错</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>主核崩溃 Fail-Safe 与 WDT 硬件复位测试</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1. 启用飞腾派底层看门狗 (FWDT)。
-2. 在主核系统崩溃或出现严重硬件级异常（如内存访问错讯导致系统挂起）时，停止喂狗。
-3. 验证看门狗超时（配置超时为 10 秒）后是否会自动触发板卡硬件重启以实现自愈。</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>硬件看门狗溢叺，触发飞腾派硬件全面冷重启。</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pass。通过模拟内核级跑飞和停止喂狗，飞腾硬件看门狗成功在 10s 超时后强制寵主从核进行硬件冷复位重启，系统自愈闭环功能完全生故　</t>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>硬件看门狗超时冷重启与 Fail-Safe 自愈测试</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>1. 飞腾底层 fwdt 硬件看门狗驱动已加载。
+2. 从核 Fail-Safe 降级接管逻辑就绪。</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>1. 模拟主核宕机失联超过 2s。
+2. 观察从核是否接管 GPIO 驱动蜂鸣器报警，并观察 10s 后系统是否执行冷重启。</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>1. 主核宕机 2s 后，从核拉高 GPIO 驱动蜂鸣器长鸣报警，并停止喂狗。
+2. 停止喂狗 10s 后，看门狗超时溢出触发处理器硬件冷重启自动重启系统。</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Pass。主核异常宕机 2s 后从核成功接管并驱动蜂鸣器长鸣，停止喂狗 10s 后成功触发飞腾芯片硬件冷重启，系统完整恢复并重新拉起，实现全面自愈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>TC-11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>DeepSeek AI 智能安全顾问接口与方框乱码规避测试</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>1. 系统网络连接正常，配置了有效的 DeepSeek API Key。
+2. 违规聚合与 OSD 渲染模块处于激活状态。</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>1. 触发违规事件，观察 DeepSeek 异步调用与整改建议返回速度。
+2. 检查 UI 界面上 DeepSeek 建议文本框中是否存在表情符号转义失败导致的方框乱码。
+3. 在 10s 内连续触发多次违规，观察界面日志是否进行聚合。</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>1. DeepSeek 异步生成整改建议，平均响应时间 &lt; 2s，且不阻塞主渲染线程。
+2. UI 界面中文显示清晰，无任何 emoji 表情符乱码方框。
+3. 多次违规事件以滑动时间窗口在 UI 大屏左下角进行数量聚合，显示清晰。</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Pass。DeepSeek API 成功异步接入并生成高质量安全整改建议，UI 界面排除了所有 emoji 乱码，且 10s 滑动时间窗口内的违规事件成功实现数量聚合展示。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="37">
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="E13:E14"/>
+    <mergeCell ref="B17:B18"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C10:C11"/>
@@ -1737,6 +1793,7 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="B13:B14"/>
+    <mergeCell ref="F17:F18"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="E6:E7"/>
@@ -1747,8 +1804,10 @@
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C17:C18"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="B4:B5"/>

--- a/Phytium_PPE_System_SourceCode/功能测试表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能测试表.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -248,6 +248,15 @@
       <color rgb="FFFF0000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -455,7 +464,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -631,6 +640,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -781,7 +817,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -877,6 +913,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1262,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="11.4416666666667" customWidth="1" style="24" min="1" max="1"/>
@@ -1274,549 +1320,636 @@
   </cols>
   <sheetData>
     <row r="1" ht="10.75" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>测试用例编号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>测试模块</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>测试前置条件</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>测试步骤</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>实测结果</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19.5" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>TC-01</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
-        <is>
-          <t>视频源热切换测试</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>程序正常运行，摄像头已连接</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>视频流采集模块</t>
+        </is>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>物理 USB 摄像头已成功挂载</t>
+        </is>
+      </c>
+      <c r="D2" s="35" t="inlineStr">
+        <is>
+          <t>1. 启动智能监控大屏系统。
+2. 观察视频源拉流帧率及 CPU 绑核规则（Core 0）。</t>
+        </is>
+      </c>
+      <c r="E2" s="35" t="inlineStr">
+        <is>
+          <t>1. 实时拉流帧率稳定在 11.4 FPS 左右。
+2. 拉流控制线程静态绑定于 Core 0 小核运行。</t>
+        </is>
+      </c>
+      <c r="F2" s="34" t="inlineStr">
+        <is>
+          <t>Pass。USB 摄像头阻塞式拉流帧率稳定，Core 0 绑核正常，系统大核未受 I/O 中断竞争影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="12.25" customFormat="1" customHeight="1" s="2">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>视频流采集模块</t>
+        </is>
+      </c>
+      <c r="C3" s="35" t="inlineStr">
+        <is>
+          <t>程序正常运行，摄像头已连接，本地包含测试视频</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>1. 在 Qt 界面点击“导入录像”导入 MP4 文件。</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>1. 画面接近无缝切换至视频文件，程序无卡顿闪退。</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
-        <is>
-          <t>画面切换瞬间平滑；视频播放完毕后终端打印回退提示，1秒内成功切回物理摄像头画面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="12.25" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="29" t="n"/>
-      <c r="B3" s="29" t="n"/>
-      <c r="C3" s="29" t="n"/>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="F3" s="34" t="inlineStr">
+        <is>
+          <t>Pass。画面切换瞬间平滑无缝；视频播放完毕后终端打印回退提示，1秒内成功切回物理摄像头画面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="13" customFormat="1" customHeight="1" s="3">
+      <c r="A4" s="36" t="n"/>
+      <c r="B4" s="36" t="n"/>
+      <c r="C4" s="36" t="n"/>
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>2. 观察视频播放完毕后的系统反应。</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>2. 视频播放完毕后，自动切回 USB 摄像头实时画面。</t>
         </is>
       </c>
-      <c r="F3" s="29" t="n"/>
-    </row>
-    <row r="4" ht="13" customFormat="1" customHeight="1" s="3">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>TC-02</t>
-        </is>
-      </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>无锁总线死锁测试</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t>系统四核满载并发运行</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="F4" s="36" t="n"/>
+    </row>
+    <row r="5" ht="20.25" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>TC-03</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>数据总线模块</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>系统多线程高并发运行</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>1. 开启 htop 监控 CPU 状态。</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>Core 2/3 大核占用率持续保持 95% 以上，Core 0 小核保持55%左右。未发生因锁死导致的程序假死。</t>
-        </is>
-      </c>
-      <c r="F4" s="31" t="inlineStr">
-        <is>
-          <t>实测系统连续运行 1 小时无崩溃。Core 2/3 稳定在 98% 算力全开，无内核态阻塞导致的主频跌落。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20.25" customFormat="1" customHeight="1" s="3">
-      <c r="A5" s="29" t="n"/>
-      <c r="B5" s="29" t="n"/>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>2. 让系统连续运行超 4 小时，观察多核并发状态。</t>
-        </is>
-      </c>
-      <c r="E5" s="29" t="n"/>
-      <c r="F5" s="29" t="n"/>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>1. Core 2/3 大核占用率持续保持 95% 以上，Core 0 小核保持 55% 左右，无线程竞争死锁。</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>Pass。基于原子屏障 of SPSC 无锁环形队列运行良好，大核算力全开（达 98%），满载运行 4 小时无假死或内核态阻塞。</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="10" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>TC-03</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>极小目标量化检测</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>输入包含远处“手套/眼镜”的画面</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>1. 让人员站在距摄像头 3-5 米外。</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t>依托 QAT 量化技术，小目标特征未塌陷，UI 界面依然能稳定画出红色违规框，置信度保持在 0.45 以上。</t>
-        </is>
-      </c>
-      <c r="F6" s="28" t="inlineStr">
-        <is>
-          <t>INT8 降维后依然精准识别远端手套目标，未发生传统 PTQ 导致的特征抹平漏报，置信度稳定在 0.52。</t>
-        </is>
-      </c>
+      <c r="A6" s="36" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>2. 让系统高负荷连续运行超 4 小时，观察多线程并发状态。</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>2. 系统连续运行无崩溃、无主频下跌。</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="n"/>
     </row>
     <row r="7" ht="20.25" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>2. 观察系统对“未戴手套”、“未戴眼镜”等小微特征的检出率。</t>
-        </is>
-      </c>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29" t="n"/>
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>TC-04</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>AI视觉推理模块</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>输入包含远处“手套/眼镜/安全帽”等小目标的画面</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>1. 让受试人员站在距摄像头 3-5 米外。</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>1. 依托 QAT 量化技术，小目标特征未塌陷，UI 界面依然能稳定画出红色违规框，置信度保持在 0.45 以上。</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>Pass。QAT INT8 模型推理精度优良，远处手套等微小特征未被截断抹平，置信度稳定在 0.52 以上。</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="19.5" customFormat="1" customHeight="1" s="3">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>TC-04</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>复杂遮挡追踪测试</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>2. 观察系统对“未戴手套”、“未戴眼镜”等微小特征的检出率。</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>2. 微小特征未发生传统 PTQ 导致的特征抹平漏报。</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="n"/>
+    </row>
+    <row r="9" ht="10.75" customFormat="1" customHeight="1" s="3">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>TC-05</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>AI视觉推理模块</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>开启 ByteTrack 追踪模块</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>1. 安排两名工人（ID:1, ID:2）在镜头前交叉走动。</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>两人交叉或被遮挡后，追踪 ID 不发生转变。防抖状态机正常工作，未触发重复的瞬间抓拍。</t>
-        </is>
-      </c>
-      <c r="F8" s="31" t="inlineStr">
-        <is>
-          <t>遮挡超 15 帧后目标重现，卡尔曼滤波成功捞回原 ID 并继续追踪。全程只会发生 ID 低概率发生跳变。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="10.75" customFormat="1" customHeight="1" s="3">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>2. 安排工人短暂走到障碍物后方再走出。</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>1. 两人交叉或被遮挡后重新出现时，追踪 ID 不发生转变。</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>Pass。复杂遮挡重现后，卡尔曼滤波成功捞回原 ID 并继续追踪，状态防抖正常，ID 未频繁跳变。</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="35.4" customFormat="1" customHeight="1" s="2">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>TC-05</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>异构通信蜂鸣器测试</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>1号小核裸机固件已加载</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>1. 模拟工人摘下安全帽（违规）。</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>1. 摘下帽子瞬间，从核 GPIO 立刻拉高，蜂鸣器长鸣。</t>
-        </is>
-      </c>
-      <c r="F10" s="32" t="inlineStr">
-        <is>
-          <t>主核下发指令至从核驱动蜂鸣器的全链路响应时间 &lt; 1 毫秒（微秒级），状态防抖基本实现，但是还是存在存在误测问题</t>
-        </is>
-      </c>
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>2. 安排工人短暂走到障碍物后方（遮挡 15 帧以上）再走出。</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>2. 避免了因为 ID 频繁跳变引起的冗余 I/O 写入。</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="n"/>
     </row>
     <row r="11" ht="10.75" customFormat="1" customHeight="1" s="2">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="29" t="n"/>
-      <c r="C11" s="29" t="n"/>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>2. 模拟工人重新戴上安全帽（合规）。</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>2. 戴上帽子瞬间，触发“洗白”，蜂鸣器停止。</t>
-        </is>
-      </c>
-      <c r="F11" s="29" t="n"/>
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>TC-06</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>软硬联动模块</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>1号小核裸机固件已加载，硬件连接正常</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>1. 模拟工人摘下安全帽（违规），观察从核蜂鸣器反应。</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>1. 摘下帽子瞬间，从核 GPIO 立刻拉高，蜂鸣器长鸣报警。</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>Pass。OpenAMP RPMsg 跨核联动顺畅，主核违规判决下发至从核驱动 GPIO 延迟 &lt; 1ms，双向防抖响应精准。</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="46.75" customFormat="1" customHeight="1" s="3">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>TC-06</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>OpenAMP 跨核报警联动与防抖边界测试</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>1.OpenAMP 底层通信链路已就绪。2.满载抗压环境:Linux端开启视频与 AI 并发推理，CPU 负载处于满载状态。</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>1.突发中断触发:物理触发火焰传感器，向从核注入低电平硬件中断。
-2.边缘抖动模拟:触发后 50ms 内瞬间撤除火源，人为制造临界电平跳变。</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>1.抢占式响应:系统无视 AI 线程满载，rx_task极速捕获中断并完成 UI 渲染，端到端延迟 &lt; 20ms。
-2.状态机防抖:无视撤除火源后的抖动干扰，UI强制锁定红色报警态500ms 后精确重置，全过程画面零闪烁。</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>火焰传感器正常运行，并且从核能向主核心发送报警信息。</t>
-        </is>
-      </c>
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>2. 模拟工人重新戴上安全帽（合规），观察从核状态。</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>2. 戴上帽子瞬间，触发“洗白”，从核蜂鸣器立即停止。</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="n"/>
     </row>
     <row r="13" ht="12.6" customFormat="1" customHeight="1" s="2">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>TC-07</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>Qt 界面渲染与监控</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>UI 界面处于主监控状态</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>1. 观察画面是否有撕裂现象。</t>
-        </is>
-      </c>
-      <c r="E13" s="26" t="inlineStr">
-        <is>
-          <t>画面通过零拷贝渲染流畅无撕裂。系统大屏温度与负载数据每 2 秒更新一次，数值精准吻合。</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>GUI 界面无卡死现象，实时帧率稳定在 11.4 FPS；解析 /proc/stat 获取的真实负载率与终端一致。</t>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>软硬联动模块</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>1. OpenAMP 底层通信链路已就绪。
+2. 主核处于 AI 推理满载状态。</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>1. 物理触发火焰传感器，向从核注入低电平硬件中断。</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>1. rx_task 极速捕获中断并完成 UI 渲染，端到端延迟 &lt; 20ms。</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>Pass。火焰传感器硬中断抢占机制测试通过。在 50ms 模拟抖动下未触发误报，Qt 界面火警弹窗显示稳定。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20.25" customFormat="1" customHeight="1" s="2">
-      <c r="A14" s="29" t="n"/>
-      <c r="B14" s="29" t="n"/>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>2. 核对侧边栏的 CPU 温度和负载百分比，与底层命令对比。</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>2. 模拟 50ms 内的临界电平抖动，观察界面稳定性。</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>2. 排除抖动干扰，UI 报警状态锁定 500ms 后重置，无闪烁。</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="n"/>
     </row>
     <row r="15" ht="32.5" customFormat="1" customHeight="1" s="3">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>TC-08</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>磁盘防洪异常注入测试</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>修改磁盘报警阈值为当前使用率</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>1. 向 /violations_data 文件夹强行拷入海量垃圾文件，使磁盘占用达到 85% 以上。</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>系统不报内存溢出崩溃，底层 statvfs 成功拦截满载事件，按时间戳准确自动删除了最旧的 20% 档案。</t>
-        </is>
-      </c>
-      <c r="F15" s="31" t="inlineStr">
-        <is>
-          <t>容量越界后触发极客级自动清洗，精准按最后写入时间 升序销毁冗余图片 1500 张，后续写盘成功。</t>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>UI交互渲染模块</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>UI 界面处于监控状态</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>1. 启动视频拉流，观察监控大屏画面是否有撕裂或相位滞后现象。</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>画面通过零拷贝图像指针进行原位映射，视频流畅无撕裂，帧率稳定在 11.4 FPS。</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>Pass。零拷贝渲染极大地降低了内存拷贝开销，视频在大屏幕原位渲染平滑流畅，帧率达到 11.4 FPS。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="10.75" customFormat="1" customHeight="1" s="3">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>2. 触发一次违规。</t>
-        </is>
-      </c>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>TC-09</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>UI交互渲染模块</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>系统处于正常运行状态</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>1. 核对侧边栏的 CPU 温度和负载百分比，与底层终端 htop 监控值对比。</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>解析 /proc/stat 与 /sys/class/thermal 获得的数据精准在 UI 看板刷新，每 2 秒自刷新且与终端一致。</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>Pass。硬件监控看板数据刷新机制正常，CPU 负载与温度动态展示无误，与底层 htop 实测完全一致。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>TC-09</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>双核通信 Active Heartbeat 心跳测试</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>TC-10</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>本地存储模块</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>触发违规事件</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>1. 模拟违规事件发生，观察专职 I/O 线程在后台执行 JPEG 编码和 CSV 写入时的 UI 流畅度。</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>异步后台队列剥离写盘，JPEG 快照与 CSV 日志顺利落盘，大屏前台渲染无卡死或跳帧现象。</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>Pass。违规抓拍与日志异步写盘机制运行良好，证据不丢失，且消除了 I/O 阻塞对前台 GUI 帧率的影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>TC-11</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="inlineStr">
+        <is>
+          <t>本地存储模块</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>violations_data 目录空间报警阈值已配</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>1. 向 violations_data 强行拷入大文件，使磁盘分区占用达到 85% 以上，触发一次新违规。</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>系统主动拦截溢出风险，按时间戳升序自动删除最旧的 20% 照片档案，后续写盘正常。</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>Pass。分区占用率超 85% 后自动触发自清洁机制，成功按时间戳升序清理 1500 张旧照片，新抓拍顺利写入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>TC-12</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>安全可靠性保障模块</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>1. 主从核通过 OpenAMP 初始化成功。
 2. 心跳监控线程 heartbeat_task 已启动，周期 500ms。</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>1. 主核正常运行时，监测从核对心跳包的应答。
-2. 在主核中人为挂起 AI 业务线程，观察心跳是否能维持或检测到失联。</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>1. 正常运行时主从核以 500ms 频率稳定收发心跳包。
-2. 主核业务异常后，能在 2s 内（4次未响应）准确检测并报警，从核串口输出失联报警日志。</t>
-        </is>
-      </c>
-      <c r="F17" s="31" t="inlineStr">
-        <is>
-          <t>Pass。真机测试表明主从核心跳收发无误。在主核人为停止心跳发送 2s 后，从核串口精准捕获失联报警，系统未发生崩溃僵死。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="29" t="n"/>
-      <c r="C18" s="29" t="n"/>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>2. 观察从核的应答状态以及失联时的动作。</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>2. 从核检测到 2s 主核心跳丢失后，打印失联日志，开启 Fail-Safe 警报，并在 10s WDT 超时后触发冷重启。</t>
-        </is>
-      </c>
-      <c r="F18" s="29" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>TC-10</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>硬件看门狗超时冷重启与 Fail-Safe 自愈测试</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>1. 监测正常运行时从核对心跳包的应答状态。</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>1. 主从核以 500ms 周期稳定发包。</t>
+        </is>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>Pass。心跳线程真机测试通过。主核人为挂起后，从核在 2s 内准确检测并报警，且串口成功打印失联日志。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>2. 在主核人为挂起 AI 业务线程，观察心跳是否丢失并验证从核报警动作。</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>2. 主核心跳丢失 2s（4次超时）后，从核串口捕获异常并打印主从失联日志。</t>
+        </is>
+      </c>
+      <c r="F20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>TC-13</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="inlineStr">
+        <is>
+          <t>安全可靠性保障模块</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>1. 飞腾底层 fwdt 硬件看门狗驱动已加载。
-2. 从核 Fail-Safe 降级接管逻辑就绪。</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>1. 模拟主核宕机失联超过 2s。
-2. 观察从核是否接管 GPIO 驱动蜂鸣器报警，并观察 10s 后系统是否执行冷重启。</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>1. 主核宕机 2s 后，从核拉高 GPIO 驱动蜂鸣器长鸣报警，并停止喂狗。
-2. 停止喂狗 10s 后，看门狗超时溢出触发处理器硬件冷重启自动重启系统。</t>
-        </is>
-      </c>
-      <c r="F19" s="31" t="inlineStr">
-        <is>
-          <t>Pass。主核异常宕机 2s 后从核成功接管并驱动蜂鸣器长鸣，停止喂狗 10s 后成功触发飞腾芯片硬件冷重启，系统完整恢复并重新拉起，实现全面自愈。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>TC-11</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>DeepSeek AI 智能安全顾问接口与方框乱码规避测试</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>1. 系统网络连接正常，配置了有效的 DeepSeek API Key。
-2. 违规聚合与 OSD 渲染模块处于激活状态。</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>1. 触发违规事件，观察 DeepSeek 异步调用与整改建议返回速度。
-2. 检查 UI 界面上 DeepSeek 建议文本框中是否存在表情符号转义失败导致的方框乱码。
-3. 在 10s 内连续触发多次违规，观察界面日志是否进行聚合。</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>1. DeepSeek 异步生成整改建议，平均响应时间 &lt; 2s，且不阻塞主渲染线程。
-2. UI 界面中文显示清晰，无任何 emoji 表情符乱码方框。
-3. 多次违规事件以滑动时间窗口在 UI 大屏左下角进行数量聚合，显示清晰。</t>
-        </is>
-      </c>
-      <c r="F20" s="31" t="inlineStr">
-        <is>
-          <t>Pass。DeepSeek API 成功异步接入并生成高质量安全整改建议，UI 界面排除了所有 emoji 乱码，且 10s 滑动时间窗口内的违规事件成功实现数量聚合展示。</t>
+2. 从核 Fail-Safe 自愈逻辑处于监听状态。</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>1. 模拟主核异常挂死导致心跳中断，监测从核接管与看门狗冷重启反应。</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>1. 心跳中断 2s 后从核接管并拉高 GPIO 驱动蜂鸣器长鸣报警，同时停止向 WDT 喂狗。
+2. 停止喂狗 10s 后 WDT 超时溢出，硬件强制复位芯片冷重启系统。</t>
+        </is>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>Pass。主核宕机后从核瞬间接管驱动蜂鸣器长鸣，WDT 超时 10s 后芯片执行硬件 cold reset 成功冷重启并恢复自愈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>TC-14</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>智能安全顾问模块</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>1. 系统网络畅通且配置了 DeepSeek API Key。
+2. 滑动窗口与 UI 日志渲染激活。</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>1. 触发违规，观察 DeepSeek 异步调用、整改建议及 UI 字符表现（规避表情符号）。
+2. 在 10s 内连续触发多次违规，观察数量聚合表现。</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>1. 异步返回整改建议，无表情符方框乱码，平均延迟 &lt; 2s。
+2. 10s 滑动时间窗口内的违规事件成功在左下角进行数量聚合。</t>
+        </is>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>Pass。DeepSeek API 成功异步接入且无 UI 乱码方框，滑动窗口违规事件数量聚合展示正常.docx。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F8:F9"/>
+  <mergeCells count="28">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="C9:C10"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A5:A6"/>
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="F9:F10"/>
     <mergeCell ref="A13:A14"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A19:A20"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Phytium_PPE_System_SourceCode/功能测试表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能测试表.xlsx
@@ -1311,15 +1311,16 @@
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="11.4416666666667" customWidth="1" style="24" min="1" max="1"/>
-    <col width="18.775" customWidth="1" style="24" min="3" max="3"/>
-    <col width="26.1083333333333" customWidth="1" style="24" min="4" max="4"/>
-    <col width="35.5583333333333" customWidth="1" style="24" min="5" max="5"/>
-    <col width="40.775" customWidth="1" style="24" min="6" max="6"/>
+    <col width="12" customWidth="1" style="24" min="1" max="1"/>
+    <col width="20" customWidth="1" style="24" min="2" max="2"/>
+    <col width="25" customWidth="1" style="24" min="3" max="3"/>
+    <col width="35" customWidth="1" style="24" min="4" max="4"/>
+    <col width="35" customWidth="1" style="24" min="5" max="5"/>
+    <col width="35" customWidth="1" style="24" min="6" max="6"/>
     <col width="35.5583333333333" customWidth="1" style="24" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="10.75" customFormat="1" customHeight="1" s="1">
+    <row r="1" ht="29" customFormat="1" customHeight="1" s="1">
       <c r="A1" s="33" t="inlineStr">
         <is>
           <t>测试用例编号</t>
@@ -1351,7 +1352,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customFormat="1" customHeight="1" s="2">
+    <row r="2" ht="46" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
           <t>TC-01</t>
@@ -1385,7 +1386,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.25" customFormat="1" customHeight="1" s="2">
+    <row r="3" ht="46" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="34" t="inlineStr">
         <is>
           <t>TC-02</t>
@@ -1417,7 +1418,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="13" customFormat="1" customHeight="1" s="3">
+    <row r="4" ht="29" customFormat="1" customHeight="1" s="3">
       <c r="A4" s="36" t="n"/>
       <c r="B4" s="36" t="n"/>
       <c r="C4" s="36" t="n"/>
@@ -1433,7 +1434,7 @@
       </c>
       <c r="F4" s="36" t="n"/>
     </row>
-    <row r="5" ht="20.25" customFormat="1" customHeight="1" s="3">
+    <row r="5" ht="46" customFormat="1" customHeight="1" s="3">
       <c r="A5" s="34" t="inlineStr">
         <is>
           <t>TC-03</t>
@@ -1465,7 +1466,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="10" customFormat="1" customHeight="1" s="2">
+    <row r="6" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A6" s="36" t="n"/>
       <c r="B6" s="36" t="n"/>
       <c r="C6" s="36" t="n"/>
@@ -1481,7 +1482,7 @@
       </c>
       <c r="F6" s="36" t="n"/>
     </row>
-    <row r="7" ht="20.25" customFormat="1" customHeight="1" s="2">
+    <row r="7" ht="46" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="34" t="inlineStr">
         <is>
           <t>TC-04</t>
@@ -1513,7 +1514,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="19.5" customFormat="1" customHeight="1" s="3">
+    <row r="8" ht="46" customFormat="1" customHeight="1" s="3">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="36" t="n"/>
       <c r="C8" s="36" t="n"/>
@@ -1529,7 +1530,7 @@
       </c>
       <c r="F8" s="36" t="n"/>
     </row>
-    <row r="9" ht="10.75" customFormat="1" customHeight="1" s="3">
+    <row r="9" ht="46" customFormat="1" customHeight="1" s="3">
       <c r="A9" s="34" t="inlineStr">
         <is>
           <t>TC-05</t>
@@ -1561,7 +1562,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="35.4" customFormat="1" customHeight="1" s="2">
+    <row r="10" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A10" s="36" t="n"/>
       <c r="B10" s="36" t="n"/>
       <c r="C10" s="36" t="n"/>
@@ -1577,7 +1578,7 @@
       </c>
       <c r="F10" s="36" t="n"/>
     </row>
-    <row r="11" ht="10.75" customFormat="1" customHeight="1" s="2">
+    <row r="11" ht="46" customFormat="1" customHeight="1" s="2">
       <c r="A11" s="34" t="inlineStr">
         <is>
           <t>TC-06</t>
@@ -1609,7 +1610,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="46.75" customFormat="1" customHeight="1" s="3">
+    <row r="12" ht="29" customFormat="1" customHeight="1" s="3">
       <c r="A12" s="36" t="n"/>
       <c r="B12" s="36" t="n"/>
       <c r="C12" s="36" t="n"/>
@@ -1625,7 +1626,7 @@
       </c>
       <c r="F12" s="36" t="n"/>
     </row>
-    <row r="13" ht="12.6" customFormat="1" customHeight="1" s="2">
+    <row r="13" ht="46" customFormat="1" customHeight="1" s="2">
       <c r="A13" s="34" t="inlineStr">
         <is>
           <t>TC-07</t>
@@ -1658,7 +1659,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="20.25" customFormat="1" customHeight="1" s="2">
+    <row r="14" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="36" t="n"/>
       <c r="C14" s="36" t="n"/>
@@ -1674,7 +1675,7 @@
       </c>
       <c r="F14" s="36" t="n"/>
     </row>
-    <row r="15" ht="32.5" customFormat="1" customHeight="1" s="3">
+    <row r="15" ht="46" customFormat="1" customHeight="1" s="3">
       <c r="A15" s="34" t="inlineStr">
         <is>
           <t>TC-08</t>
@@ -1706,7 +1707,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="10.75" customFormat="1" customHeight="1" s="3">
+    <row r="16" ht="46" customFormat="1" customHeight="1" s="3">
       <c r="A16" s="34" t="inlineStr">
         <is>
           <t>TC-09</t>
@@ -1738,7 +1739,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="46" customHeight="1" s="24">
       <c r="A17" s="34" t="inlineStr">
         <is>
           <t>TC-10</t>
@@ -1770,7 +1771,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="46" customHeight="1" s="24">
       <c r="A18" s="34" t="inlineStr">
         <is>
           <t>TC-11</t>
@@ -1802,7 +1803,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="63" customHeight="1" s="24">
       <c r="A19" s="34" t="inlineStr">
         <is>
           <t>TC-12</t>
@@ -1835,7 +1836,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="46" customHeight="1" s="24">
       <c r="A20" s="36" t="n"/>
       <c r="B20" s="36" t="n"/>
       <c r="C20" s="36" t="n"/>
@@ -1851,7 +1852,7 @@
       </c>
       <c r="F20" s="36" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="63" customHeight="1" s="24">
       <c r="A21" s="34" t="inlineStr">
         <is>
           <t>TC-13</t>
@@ -1876,7 +1877,7 @@
       <c r="E21" s="35" t="inlineStr">
         <is>
           <t>1. 心跳中断 2s 后从核接管并拉高 GPIO 驱动蜂鸣器长鸣报警，同时停止向 WDT 喂狗。
-2. 停止喂狗 10s 后 WDT 超时溢出，硬件强制复位芯片冷重启系统。</t>
+2. 停止喂狗 10s 后 WDT 超时溢出，硬件强制复位芯片 cold reset 冷重启系统。</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
@@ -1885,7 +1886,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="63" customHeight="1" s="24">
       <c r="A22" s="34" t="inlineStr">
         <is>
           <t>TC-14</t>
@@ -1916,15 +1917,15 @@
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>Pass。DeepSeek API 成功异步接入且无 UI 乱码方框，滑动窗口违规事件数量聚合展示正常.docx。</t>
+          <t>Pass。DeepSeek API 成功异步接入且无 UI 乱码方框，滑动窗口违规事件数量聚合展示正常。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
     <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A7:A8"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="A7:A8"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C9:C10"/>
@@ -1932,8 +1933,8 @@
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="B19:B20"/>
+    <mergeCell ref="F13:F14"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="F13:F14"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A13:A14"/>
@@ -1941,8 +1942,8 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C19:C20"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="C19:C20"/>
     <mergeCell ref="F19:F20"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="C3:C4"/>

--- a/Phytium_PPE_System_SourceCode/功能测试表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能测试表.xlsx
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F12" s="36" t="n"/>
     </row>
-    <row r="13" ht="46" customFormat="1" customHeight="1" s="2">
+    <row r="13" ht="63" customFormat="1" customHeight="1" s="2">
       <c r="A13" s="34" t="inlineStr">
         <is>
           <t>TC-07</t>
@@ -1634,43 +1634,43 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>软硬联动模块</t>
+          <t>软硬联动与环境检测</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
           <t>1. OpenAMP 底层通信链路已就绪。
-2. 主核处于 AI 推理满载状态。</t>
+2. 从核已接入火焰、有害气体及温湿度传感器并满载运行。</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>1. 物理触发火焰传感器，向从核注入低电平硬件中断。</t>
+          <t>1. 物理触发火焰与有害气体传感器，向从核注入硬件中断与 ADC 模拟数据。</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>1. rx_task 极速捕获中断并完成 UI 渲染，端到端延迟 &lt; 20ms。</t>
+          <t>1. rx_task 极速捕获中断并渲染 UI，报警端到端延迟 &lt; 20ms，有害气体 ADC 采样值精准。</t>
         </is>
       </c>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>Pass。火焰传感器硬中断抢占机制测试通过。在 50ms 模拟抖动下未触发误报，Qt 界面火警弹窗显示稳定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="29" customFormat="1" customHeight="1" s="2">
+          <t>Pass。火焰与有害气体硬中断抢占机制测试通过。在 50ms 模拟抖动下无闪烁；温湿度环境数据大屏实时刷新无误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customFormat="1" customHeight="1" s="2">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="36" t="n"/>
       <c r="C14" s="36" t="n"/>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>2. 模拟 50ms 内的临界电平抖动，观察界面稳定性。</t>
+          <t>2. 模拟 50ms 内的临界电平抖动，并读取 AHT20 温湿度传感器数据，观察界面显示。</t>
         </is>
       </c>
       <c r="E14" s="35" t="inlineStr">
         <is>
-          <t>2. 排除抖动干扰，UI 报警状态锁定 500ms 后重置，无闪烁。</t>
+          <t>2. 排除抖动干扰，报警状态锁定 500ms 后重置，温湿度环境数据大屏每 2s 稳定刷新，无闪烁现象。</t>
         </is>
       </c>
       <c r="F14" s="36" t="n"/>
@@ -1877,7 +1877,7 @@
       <c r="E21" s="35" t="inlineStr">
         <is>
           <t>1. 心跳中断 2s 后从核接管并拉高 GPIO 驱动蜂鸣器长鸣报警，同时停止向 WDT 喂狗。
-2. 停止喂狗 10s 后 WDT 超时溢出，硬件强制复位芯片 cold reset 冷重启系统。</t>
+2. 停止喂狗 10s 后 WDT 超时溢出，硬件强制复位芯片冷重启系统。</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">

--- a/Phytium_PPE_System_SourceCode/功能测试表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能测试表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="10480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27950" windowHeight="12280" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新建 Text Document" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -40,13 +40,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -397,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -431,19 +424,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -593,22 +573,25 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1">
@@ -617,40 +600,37 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1">
@@ -662,7 +642,7 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="1">
@@ -674,7 +654,7 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1">
@@ -686,7 +666,7 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="1">
@@ -698,7 +678,7 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1">
@@ -710,7 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="1">
@@ -723,7 +703,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -740,36 +720,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1155,14 +1112,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="34.9916666666667" defaultRowHeight="128" customHeight="1"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="34.9916666666667" customWidth="1" style="4" min="1" max="7"/>
-    <col width="34.9916666666667" customWidth="1" style="4" min="8" max="16384"/>
+    <col width="12" customWidth="1" style="4" min="1" max="1"/>
+    <col width="20" customWidth="1" style="4" min="2" max="2"/>
+    <col width="25" customWidth="1" style="4" min="3" max="3"/>
+    <col width="35" customWidth="1" style="4" min="4" max="6"/>
+    <col width="35.5583333333333" customWidth="1" style="4" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
+    <row r="1" ht="29" customFormat="1" customHeight="1" s="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>测试用例编号</t>
@@ -1193,628 +1153,582 @@
           <t>实测结果</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            演示图片</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="7" t="inlineStr">
+    </row>
+    <row r="2" ht="46" customFormat="1" customHeight="1" s="2">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>TC-01</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>视频流采集模块</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>物理 USB 摄像头已成功挂载</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>1. 启动智能监控大屏系统。
 2. 观察视频源拉流帧率及 CPU 绑核规则（Core 0）。</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>1. 实时拉流帧率稳定在 11.4 FPS 左右。
 2. 拉流控制线程静态绑定于 Core 0 小核运行。</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Pass。USB 摄像头阻塞式拉流帧率稳定，Core 0 绑核正常，系统大核未受 I/O 中断竞争影响。</t>
         </is>
       </c>
-      <c r="G2" s="9">
-        <f>_xlfn.DISPIMG("ID_57E01F984F6E4E94BF9CC091F8A203E6",1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="7" t="inlineStr">
+    </row>
+    <row r="3" ht="46" customFormat="1" customHeight="1" s="2">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>TC-02</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>视频流采集模块</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>程序正常运行，摄像头已连接，本地包含测试视频</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>1. 在 Qt 界面点击“导入录像”导入 MP4 文件。</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>1. 画面接近无缝切换至视频文件，程序无卡顿闪退。</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Pass。画面切换瞬间平滑无缝；视频播放完毕后终端打印回退提示，1秒内成功切回物理摄像头画面。</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="3">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
+    </row>
+    <row r="4" ht="29" customFormat="1" customHeight="1" s="3">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>2. 观察视频播放完毕后的系统反应。</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>2. 视频播放完毕后，自动切回 USB 摄像头实时画面。</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="3">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="F4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="46" customFormat="1" customHeight="1" s="3">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>TC-03</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>数据总线模块</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>系统多线程高并发运行</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>1. 开启 htop 监控 CPU 状态。</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>1. Core 2/3 大核占用率持续保持 95% 以上，Core 0 小核保持 55% 左右，无线程竞争死锁。</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Pass。基于原子屏障 of SPSC 无锁环形队列运行良好，大核算力全开（达 98%），满载运行 4 小时无假死或内核态阻塞。</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-    </row>
-    <row r="6" customFormat="1" s="2">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="8" t="inlineStr">
+    </row>
+    <row r="6" ht="29" customFormat="1" customHeight="1" s="2">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2. 让系统高负荷连续运行超 4 小时，观察多线程并发状态。</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>2. 系统连续运行无崩溃、无主频下跌。</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="9" t="n"/>
-    </row>
-    <row r="7" customFormat="1" s="2">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="46" customFormat="1" customHeight="1" s="2">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>TC-04</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>AI视觉推理模块</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>输入包含远处“手套/眼镜/安全帽”等小目标的画面</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>1. 让受试人员站在距摄像头 3-5 米外。</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>1. 依托 QAT 量化技术，小目标特征未塌陷，UI 界面依然能稳定画出红色违规框，置信度保持在 0.45 以上。</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Pass。QAT INT8 模型推理精度优良，远处手套等微小特征未被截断抹平，置信度稳定在 0.52 以上。</t>
         </is>
       </c>
-      <c r="G7" s="17">
-        <f>_xlfn.DISPIMG("ID_D3CCB59980184FBA946759AEEA1E0D39",1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="3">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
+    </row>
+    <row r="8" ht="46" customFormat="1" customHeight="1" s="3">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>2. 观察系统对“未戴手套”、“未戴眼镜”等微小特征的检出率。</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>2. 微小特征未发生传统 PTQ 导致的特征抹平漏报。</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-    </row>
-    <row r="9" customFormat="1" s="3">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="F8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="46" customFormat="1" customHeight="1" s="3">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>TC-05</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>AI视觉推理模块</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>开启 ByteTrack 追踪模块</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>1. 安排两名工人（ID:1, ID:2）在镜头前交叉走动。</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>1. 两人交叉或被遮挡后重新出现时，追踪 ID 不发生转变。</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Pass。复杂遮挡重现后，卡尔曼滤波成功捞回原 ID 并继续追踪，状态防抖正常，ID 未频繁跳变。</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-    </row>
-    <row r="10" customFormat="1" s="2">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
+    </row>
+    <row r="10" ht="29" customFormat="1" customHeight="1" s="2">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>2. 安排工人短暂走到障碍物后方（遮挡 15 帧以上）再走出。</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>2. 避免了因为 ID 频繁跳变引起的冗余 I/O 写入。</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="9" t="n"/>
-    </row>
-    <row r="11" customFormat="1" s="2">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="F10" s="8" t="n"/>
+    </row>
+    <row r="11" ht="46" customFormat="1" customHeight="1" s="2">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>TC-06</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>软硬联动模块</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>1号小核裸机固件已加载，硬件连接正常</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>1. 模拟工人摘下安全帽（违规），观察从核蜂鸣器反应。</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>1. 摘下帽子瞬间，从核 GPIO 立刻拉高，蜂鸣器长鸣报警。</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Pass。OpenAMP RPMsg 跨核联动顺畅，主核违规判决下发至从核驱动 GPIO 延迟 &lt; 1ms，双向防抖响应精准。</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="n"/>
-    </row>
-    <row r="12" customFormat="1" s="3">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Pass。从核终端成功打印裸机固件加载与 OpenAMP 握手就绪日志；OpenAMP RPMsg 跨核联动顺畅，主核违规判决下发至从核驱动 GPIO 延迟 &lt; 1ms，双向防抖响应精准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="29" customFormat="1" customHeight="1" s="3">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>2. 模拟工人重新戴上安全帽（合规），观察从核状态。</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>2. 戴上帽子瞬间，触发“洗白”，从核蜂鸣器立即停止。</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="11" t="n"/>
-    </row>
-    <row r="13" customFormat="1" s="2">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="F12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="63" customFormat="1" customHeight="1" s="2">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>TC-07</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>软硬联动与环境检测</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>1. OpenAMP 底层通信链路已就绪。
 2. 从核已接入火焰、有害气体及温湿度传感器并满载运行。</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>1. 物理触发火焰与有害气体传感器，向从核注入硬件中断与 状态数字信号。</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>1. rx_task 极速捕获中断并渲染 UI，报警端到端延迟 &lt; 20ms，有害气体状态读取精准。</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>1. 物理触发火焰与有害气体传感器，向从核注入硬件中断与 ADC 模拟数据。</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>1. rx_task 极速捕获中断并渲染 UI，报警端到端延迟 &lt; 20ms，有害气体 ADC 采样值精准。</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Pass。火焰与有害气体硬中断抢占机制测试通过。在 50ms 模拟抖动下无闪烁；温湿度环境数据大屏实时刷新无误。</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n"/>
-    </row>
-    <row r="14" customFormat="1" s="2">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
+    </row>
+    <row r="14" ht="46" customFormat="1" customHeight="1" s="2">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>2. 模拟 50ms 内的临界电平抖动，并读取 AHT20 温湿度传感器数据，观察界面显示。</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>2. 排除抖动干扰，报警状态锁定 500ms 后重置，温湿度环境数据大屏每 2s 稳定刷新，无闪烁现象。</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="9" t="n"/>
-    </row>
-    <row r="15" customFormat="1" s="3">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15" ht="46" customFormat="1" customHeight="1" s="3">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>TC-08</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>UI交互渲染模块</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>UI 界面处于监控状态</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>1. 启动视频拉流，观察监控大屏画面是否有撕裂或相位滞后现象。</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>画面通过零拷贝图像指针进行原位映射，视频流畅无撕裂，帧率稳定在 11.4 FPS。</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Pass。零拷贝渲染极大地降低了内存拷贝开销，视频在大屏幕原位渲染平滑流畅，帧率达到 11.4 FPS。</t>
         </is>
       </c>
-      <c r="G15" s="11">
-        <f>_xlfn.DISPIMG("ID_5CCA75F96B8F45158220BBAB5EA516F5",1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="1" s="3">
-      <c r="A16" s="7" t="inlineStr">
+    </row>
+    <row r="16" ht="46" customFormat="1" customHeight="1" s="3">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>TC-09</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>UI交互渲染模块</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>系统处于正常运行状态</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>1. 核对侧边栏的 CPU 温度和负载百分比，与底层终端 htop 监控值对比。</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>解析 /proc/stat 与 /sys/class/thermal 获得的数据精准在 UI 看板刷新，每 2 秒自刷新且与终端一致。</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Pass。硬件监控看板数据刷新机制正常，CPU 负载与温度动态展示无误，与底层 htop 实测完全一致。</t>
         </is>
       </c>
-      <c r="G16" s="11">
-        <f>_xlfn.DISPIMG("ID_C3B7A559F5BA4AEA991BC91047719634",1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" s="4">
-      <c r="A17" s="7" t="inlineStr">
+    </row>
+    <row r="17" ht="46" customHeight="1" s="4">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>TC-10</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>本地存储模块</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>触发违规事件</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>1. 模拟违规事件发生，观察专职 I/O 线程在后台执行 JPEG 编码和 CSV 写入时的 UI 流畅度。</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>异步后台队列剥离写盘，JPEG 快照与 CSV 日志顺利落盘，大屏前台渲染无卡死或跳帧现象。</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Pass。违规抓拍与日志异步写盘机制运行良好，证据不丢失，且消除了 I/O 阻塞对前台 GUI 帧率的影响。</t>
         </is>
       </c>
-      <c r="G17" s="14" t="n"/>
-    </row>
-    <row r="18" s="4">
-      <c r="A18" s="7" t="inlineStr">
+    </row>
+    <row r="18" ht="46" customHeight="1" s="4">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>TC-11</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>本地存储模块</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>violations_data 目录空间报警阈值已配</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>1. 向 violations_data 强行拷入大文件，使磁盘分区占用达到 85% 以上，触发一次新违规。</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>系统主动拦截溢出风险，按时间戳升序自动删除最旧的 20% 照片档案，后续写盘正常。</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Pass。分区占用率超 85% 后自动触发自清洁机制，成功按时间戳升序清理 1500 张旧照片，新抓拍顺利写入。</t>
         </is>
       </c>
-      <c r="G18" s="14" t="n"/>
-    </row>
-    <row r="19" s="4">
-      <c r="A19" s="7" t="inlineStr">
+    </row>
+    <row r="19" ht="63" customHeight="1" s="4">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>TC-12</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>安全可靠性保障模块</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>1. 主从核通过 OpenAMP 初始化成功。
 2. 心跳监控线程 heartbeat_task 已启动，周期 500ms。</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>1. 监测正常运行时从核对心跳包的应答状态。</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>1. 主从核以 500ms 周期稳定发包。</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Pass。心跳线程真机测试通过。主核人为挂起后，从核在 2s 内准确检测并报警，且串口成功打印失联日志。</t>
         </is>
       </c>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="20" s="4">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="8" t="inlineStr">
+    </row>
+    <row r="20" ht="46" customHeight="1" s="4">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>2. 在主核人为挂起 AI 业务线程，观察心跳是否丢失并验证从核报警动作。</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>2. 主核心跳丢失 2s（4次超时）后，从核串口捕获异常并打印主从失联日志。</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="14" t="n"/>
-    </row>
-    <row r="21" s="4">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="63" customHeight="1" s="4">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>TC-13</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>安全可靠性保障模块</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>1. 飞腾底层 fwdt 硬件看门狗驱动已加载。
 2. 从核 Fail-Safe 自愈逻辑处于监听状态。</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>1. 模拟主核异常挂死导致心跳中断，监测从核接管与看门狗冷重启反应。</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>1. 心跳中断 2s 后从核接管并停止向 WDT 喂狗。
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>1. 心跳中断 2s 后从核接管并拉高 GPIO 驱动蜂鸣器长鸣报警，同时停止向 WDT 喂狗。
 2. 停止喂狗 10s 后 WDT 超时溢出，硬件强制复位芯片冷重启系统。</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Pass。主核宕机后从核瞬间接管，WDT 超时 10s 后芯片执行硬件 cold reset 成功冷重启并恢复自愈。</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22" s="4">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Pass。主核宕机后从核瞬间接管驱动蜂鸣器长鸣，WDT 超时 10s 后芯片执行硬件 cold reset 成功冷重启并恢复自愈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="63" customHeight="1" s="4">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>TC-14</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>智能安全顾问模块</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>1. 系统网络畅通且配置了 DeepSeek API Key。
 2. 滑动窗口与 UI 日志渲染激活。</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>1. 触发违规，观察 DeepSeek 异步调用、整改建议及 UI 字符表现（规避表情符号）。
 2. 在 10s 内连续触发多次违规，观察数量聚合表现。</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>1. 异步返回整改建议，无表情符方框乱码，平均延迟 &lt; 2s。
 2. 10s 滑动时间窗口内的违规事件成功在左下角进行数量聚合。</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Pass。DeepSeek API 成功异步接入且无 UI 乱码方框，滑动窗口违规事件数量聚合展示正常。</t>
         </is>
       </c>
-      <c r="G22" s="14">
-        <f>_xlfn.DISPIMG("ID_FCE31C0D9DAB4076A916FF649E50AA12",1)</f>
-        <v/>
-      </c>
-      <c r="H22" s="16">
-        <f>_xlfn.DISPIMG("ID_B3F92420C4A14E358C5A8D6CBE2B6619",1)</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G7:G8"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B13:B14"/>
@@ -1828,8 +1742,8 @@
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="F11:F12"/>
+    <mergeCell ref="A19:A20"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A19:A20"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="F19:F20"/>

--- a/Phytium_PPE_System_SourceCode/功能测试表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能测试表.xlsx
@@ -1447,12 +1447,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1. 物理触发火焰与有害气体传感器，向从核注入硬件中断与 ADC 模拟数据。</t>
+          <t>1. 物理触发火焰与有害气体传感器，向从核注入硬件中断与 状态数字信号。</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>1. rx_task 极速捕获中断并渲染 UI，报警端到端延迟 &lt; 20ms，有害气体 ADC 采样值精准。</t>
+          <t>1. rx_task 极速捕获中断并渲染 UI，报警端到端延迟 &lt; 20ms，有害气体状态读取精准。</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1678,13 +1678,13 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>1. 心跳中断 2s 后从核接管并拉高 GPIO 驱动蜂鸣器长鸣报警，同时停止向 WDT 喂狗。
+          <t>1. 心跳中断 2s 后从核接管并停止向 WDT 喂狗。
 2. 停止喂狗 10s 后 WDT 超时溢出，硬件强制复位芯片冷重启系统。</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Pass。主核宕机后从核瞬间接管驱动蜂鸣器长鸣，WDT 超时 10s 后芯片执行硬件 cold reset 成功冷重启并恢复自愈。</t>
+          <t>Pass。主核宕机后从核瞬间接管，WDT 超时 10s 后芯片执行硬件 cold reset 成功冷重启并恢复自愈。</t>
         </is>
       </c>
     </row>

--- a/Phytium_PPE_System_SourceCode/功能测试表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能测试表.xlsx
@@ -1172,19 +1172,21 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>1. 启动智能监控大屏系统。
-2. 观察视频源拉流帧率及 CPU 绑核规则（Core 0）。</t>
+          <t>1. 启动程序前，执行 v4l2-ctl --list-devices 检查底层摄像头挂载状态。
+2. 启动智能监控大屏系统。
+3. 观察视频源拉流帧率及 CPU 绑核规则（Core 0）。</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>1. 实时拉流帧率稳定在 11.4 FPS 左右。
-2. 拉流控制线程静态绑定于 Core 0 小核运行。</t>
+          <t>1. 终端明确打印出 USB Camera 的 /dev/video* 挂载节点，底层识别正常。
+2. 实时拉流帧率稳定在 11.4 FPS 左右。
+3. 拉流控制线程静态绑定于 Core 0 小核运行。</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Pass。USB 摄像头阻塞式拉流帧率稳定，Core 0 绑核正常，系统大核未受 I/O 中断竞争影响。</t>
+          <t>Pass。启动前终端自检输出清晰的 USB 摄像头节点列表；USB 摄像头阻塞式拉流帧率稳定，Core 0 绑核正常，系统大核未受 I/O 中断竞争影响。</t>
         </is>
       </c>
     </row>

--- a/Phytium_PPE_System_SourceCode/功能测试表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能测试表.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Pass。从核终端成功打印裸机固件加载与 OpenAMP 握手就绪日志；OpenAMP RPMsg 跨核联动顺畅，主核违规判决下发至从核驱动 GPIO 延迟 &lt; 1ms，双向防抖响应精准。</t>
+          <t>Pass。从核终端打印握手就绪日志，OpenAMP 联动顺畅；经过示波器精密测量，主核下发违规判决至从核响应的物理时延平均值仅为 42.84 微秒 (μs)，远低于 1 毫秒 (ms) 的设计指标，实现了微秒级极速制动。</t>
         </is>
       </c>
     </row>
